--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE1B7C6-16C5-480E-BEFD-2B9F23FB8950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -18,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
   <si>
     <t>48987</t>
   </si>
@@ -83,9 +89,6 @@
     <t>436552</t>
   </si>
   <si>
-    <t>436555</t>
-  </si>
-  <si>
     <t>436551</t>
   </si>
   <si>
@@ -119,16 +122,25 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Contable</t>
+  </si>
+  <si>
+    <t>Estados financieros</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a la contabilidad, que forma parte de la cuenta pública.</t>
   </si>
   <si>
     <t>Programático</t>
@@ -137,21 +149,12 @@
     <t>Cuenta pública</t>
   </si>
   <si>
+    <t>Subdirección de Planeación y Evaluación, Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
     <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a lo programático, que forma parte de la cuenta pública.</t>
   </si>
   <si>
-    <t>Contable</t>
-  </si>
-  <si>
-    <t>Estados financieros</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a la contabilidad, que forma parte de la cuenta pública.</t>
-  </si>
-  <si>
     <t>Presupuestal</t>
   </si>
   <si>
@@ -161,40 +164,37 @@
     <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente al presupuesto, que forma parte de la cuenta pública.</t>
   </si>
   <si>
-    <t>EDACE9265CD82445E4FF2A6805EE0C07</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Contable/Informaci%c3%b3n%20Contable.pdf</t>
-  </si>
-  <si>
-    <t>20/07/2023</t>
-  </si>
-  <si>
-    <t>35538918972DB88B8BD59C35FFC340FB</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Presupuestal/Informaci%c3%b3n%20Presupuestal.pdf</t>
-  </si>
-  <si>
-    <t>7B80B6D42E29AA0C6DC2A909935347D8</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informaci%c3%b3n%20Program%c3%a1tica/Informaci%c3%b3n%20Program%c3%a1tica.pdf</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación, Departamento de Programación y Presupuesto</t>
+    <t>BB1C4221C990FE994C0194551E0C9218</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Programatica.pdf</t>
+  </si>
+  <si>
+    <t>19/07/2024</t>
+  </si>
+  <si>
+    <t>C740AF06A96CAD0487EF0DDC6BEC4DD6</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
+    <t>520E181821688538124AF2846F0A13CB</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Contable.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -290,6 +290,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -305,44 +308,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -370,14 +373,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -405,6 +425,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -416,193 +453,168 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="67.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="195" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="93.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="217.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="169.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="75.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="217.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -619,7 +631,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -634,7 +646,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -660,16 +672,13 @@
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -700,13 +709,10 @@
       <c r="K5" t="s">
         <v>22</v>
       </c>
-      <c r="L5" t="s">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -718,160 +724,147 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A6:K6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -880,7 +873,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E195" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -889,23 +882,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXI/LTAIPT_A63F31B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE1B7C6-16C5-480E-BEFD-2B9F23FB8950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39723B57-8A15-430F-B490-A5B1BE83F82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,67 +128,67 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>A2E3E97FDA964F297779F4B79BBCD452</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>Contable</t>
   </si>
   <si>
     <t>Estados financieros</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Contable.pdf</t>
+  </si>
+  <si>
     <t>Departamento de Contabilidad</t>
   </si>
   <si>
+    <t>19/10/2024</t>
+  </si>
+  <si>
     <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a la contabilidad, que forma parte de la cuenta pública.</t>
   </si>
   <si>
+    <t>CDCB4A56044B948B9453077633C39983</t>
+  </si>
+  <si>
     <t>Programático</t>
   </si>
   <si>
     <t>Cuenta pública</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Programatica.pdf</t>
+  </si>
+  <si>
     <t>Subdirección de Planeación y Evaluación, Departamento de Programación y Presupuesto</t>
   </si>
   <si>
     <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente a lo programático, que forma parte de la cuenta pública.</t>
   </si>
   <si>
+    <t>15B51F4876A2B7749922E65AC165E2BF</t>
+  </si>
+  <si>
     <t>Presupuestal</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/3er%20Trimestre/Informacion%20Presupuestal.pdf</t>
+  </si>
+  <si>
     <t>Departamento de Programación y Presupuesto</t>
   </si>
   <si>
     <t>La Secretaría de Finanzas no cuenta con vínculo para la públicación de dicha información, debido a que el Colegio de Bachilleres del Estado de Tlaxcala pública en su sitio oficial la información referente al presupuesto, que forma parte de la cuenta pública.</t>
-  </si>
-  <si>
-    <t>BB1C4221C990FE994C0194551E0C9218</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Programatica.pdf</t>
-  </si>
-  <si>
-    <t>19/07/2024</t>
-  </si>
-  <si>
-    <t>C740AF06A96CAD0487EF0DDC6BEC4DD6</t>
-  </si>
-  <si>
-    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Presupuestal.pdf</t>
-  </si>
-  <si>
-    <t>520E181821688538124AF2846F0A13CB</t>
-  </si>
-  <si>
-    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Programacion%20y%20Presupuesto/2do%20Trimestre/Informacion%20Contable.pdf</t>
   </si>
 </sst>
 </file>
@@ -759,107 +759,107 @@
     </row>
     <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="J10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -873,7 +873,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E195" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E193" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -888,17 +888,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
